--- a/Result/profitability/7584.xlsx
+++ b/Result/profitability/7584.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM22"/>
+  <dimension ref="A1:AM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3224,6 +3224,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>7584</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>254</v>
+      </c>
+      <c r="D23" t="n">
+        <v>147</v>
+      </c>
+      <c r="E23" t="n">
+        <v>107</v>
+      </c>
+      <c r="F23" t="n">
+        <v>42.06</v>
+      </c>
+      <c r="G23" t="n">
+        <v>8</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3.27%</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-0.1025</v>
+      </c>
+      <c r="N23" t="n">
+        <v>41.77</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-1.113821138211382</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.2706948640483384</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-1.148936170212766</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.740000000000002</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.0696846388606307</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK23" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
